--- a/tracking_forms/047_running_log_form--tracking_forms.xlsx
+++ b/tracking_forms/047_running_log_form--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>distance</t>
+          <t>distance_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>distance</t>
+          <t>Distance 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pace</t>
+          <t>pace_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>pace</t>
+          <t>Pace 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>calories_burned</t>
+          <t>calories_burned_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>calories_burned</t>
+          <t>Calories Burned 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1053,44 +1053,10 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>runkeeper</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>Runkeeper</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>apps_connected_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>google_fit</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Google Fit</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>apps_connected_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
